--- a/허브누리_레시피_목록_상세_p3of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p3of6_썸네일.xlsx
@@ -3314,7 +3314,7 @@
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="762000"/>
+    <ext cx="1047750" cy="752475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="127" name="Image 127" descr="Picture"/>
@@ -9139,7 +9139,7 @@
       <row>243</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="360" name="Image 360" descr="Picture"/>
@@ -15389,7 +15389,7 @@
       <row>448</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="610" name="Image 610" descr="Picture"/>
@@ -18514,7 +18514,7 @@
       <row>578</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="733425"/>
+    <ext cx="1047750" cy="742950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="735" name="Image 735" descr="Picture"/>
